--- a/exports/GODREJCP_full_report.xlsx
+++ b/exports/GODREJCP_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>2</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44572.38541666666</v>
+        <v>44572.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>919.65</v>
+        <v>916.3</v>
       </c>
       <c r="I2" t="n">
         <v>918.845</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.91</v>
+        <v>-2.27</v>
       </c>
       <c r="L2" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="M2" t="n">
         <v>-0</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>4.72</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44594.55208333334</v>
+        <v>44595.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>911.25</v>
+        <v>927.9</v>
       </c>
       <c r="I3" t="n">
         <v>913.9406297373237</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>0.55</v>
+        <v>-1.27</v>
       </c>
       <c r="L3" t="n">
         <v>3.46</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.54</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44600.38541666666</v>
+        <v>44600.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>878.95</v>
+        <v>875.5</v>
       </c>
       <c r="I4" t="n">
         <v>878.3508305747675</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.28</v>
+        <v>-5.65</v>
       </c>
       <c r="L4" t="n">
         <v>5.84</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.67</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44634.55208333334</v>
+        <v>44635.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>711.4</v>
+        <v>734.2</v>
       </c>
       <c r="I5" t="n">
         <v>729.7830802719349</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>18.74</v>
+        <v>16.14</v>
       </c>
       <c r="L5" t="n">
         <v>2.13</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>8.59</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44641.55208333334</v>
+        <v>44642.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>721.9</v>
+        <v>696.85</v>
       </c>
       <c r="I6" t="n">
         <v>705.0997948411833</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.68</v>
+        <v>-5.09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.35</v>
+        <v>5.85</v>
       </c>
       <c r="M6" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="N6" t="n">
         <v>3.62</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>9.58</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44650.55208333334</v>
+        <v>44651.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>727.25</v>
+        <v>746</v>
       </c>
       <c r="I7" t="n">
         <v>730.9497485897562</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.36</v>
+        <v>-7.05</v>
       </c>
       <c r="L7" t="n">
-        <v>5.12</v>
+        <v>7.56</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>7.53</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>795.15</v>
+        <v>754.8</v>
       </c>
       <c r="I8" t="n">
         <v>762.0590880967367</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>6.59</v>
+        <v>1.18</v>
       </c>
       <c r="L8" t="n">
         <v>2.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0.53</v>
+        <v>3.67</v>
       </c>
       <c r="N8" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="O8" t="n">
         <v>2.58</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44693.55208333334</v>
+        <v>44694.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>768.5</v>
+        <v>826.45</v>
       </c>
       <c r="I9" t="n">
         <v>810.1835535387937</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.82</v>
+        <v>-9.49</v>
       </c>
       <c r="L9" t="n">
-        <v>7.05</v>
+        <v>9.57</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9</v>
+        <v>1.46</v>
       </c>
       <c r="N9" t="n">
-        <v>3.11</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
         <v>-3.67</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>11.75</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44700.55208333334</v>
+        <v>44701.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>796</v>
+        <v>767.45</v>
       </c>
       <c r="I10" t="n">
         <v>767.7316863116596</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.68</v>
+        <v>-7.14</v>
       </c>
       <c r="L10" t="n">
-        <v>6.58</v>
+        <v>7.72</v>
       </c>
       <c r="M10" t="n">
-        <v>1.55</v>
+        <v>2.64</v>
       </c>
       <c r="N10" t="n">
-        <v>4.09</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
         <v>3.65</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.28</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44734.55208333334</v>
+        <v>44735.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>761</v>
+        <v>771.9</v>
       </c>
       <c r="I11" t="n">
         <v>765.4574890953224</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K11" t="n">
-        <v>0.84</v>
+        <v>-0.58</v>
       </c>
       <c r="L11" t="n">
         <v>4.29</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.99</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44768.38541666666</v>
+        <v>44768.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>853.5</v>
+        <v>838</v>
       </c>
       <c r="I12" t="n">
         <v>840.1434833571619</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K12" t="n">
-        <v>10.57</v>
+        <v>8.56</v>
       </c>
       <c r="L12" t="n">
         <v>2.97</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>6.29</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44785.55208333334</v>
+        <v>44789.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>865</v>
+        <v>888.7</v>
       </c>
       <c r="I13" t="n">
         <v>882.4317105124295</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>17</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.22</v>
+        <v>-6.05</v>
       </c>
       <c r="L13" t="n">
-        <v>5.49</v>
+        <v>11.9</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>2.28</v>
       </c>
       <c r="N13" t="n">
-        <v>2.41</v>
+        <v>2.87</v>
       </c>
       <c r="O13" t="n">
         <v>-3.18</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.81</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>925.8</v>
+        <v>896.9</v>
       </c>
       <c r="I14" t="n">
         <v>899.7734174263149</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K14" t="n">
-        <v>4.17</v>
+        <v>0.92</v>
       </c>
       <c r="L14" t="n">
         <v>1.43</v>
@@ -1239,7 +1406,7 @@
         <v>1.52</v>
       </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>3.28</v>
       </c>
       <c r="O14" t="n">
         <v>2.87</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.62</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44876.55208333334</v>
+        <v>44879.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>819.9</v>
+        <v>844.4</v>
       </c>
       <c r="I15" t="n">
         <v>841.201259095507</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K15" t="n">
-        <v>8.59</v>
+        <v>5.85</v>
       </c>
       <c r="L15" t="n">
         <v>4.02</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.43</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44907.55208333334</v>
+        <v>44908.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>893</v>
+        <v>880.55</v>
       </c>
       <c r="I16" t="n">
         <v>889.31923169327</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K16" t="n">
-        <v>5.76</v>
+        <v>4.28</v>
       </c>
       <c r="L16" t="n">
         <v>3.17</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>6.13</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44931.38541666666</v>
+        <v>44931.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>911.75</v>
+        <v>918.15</v>
       </c>
       <c r="I17" t="n">
         <v>913.4788843078029</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.54</v>
+        <v>-4.27</v>
       </c>
       <c r="L17" t="n">
-        <v>4.06</v>
+        <v>4.57</v>
       </c>
       <c r="M17" t="n">
         <v>0.72</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.21</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>914</v>
+        <v>899.45</v>
       </c>
       <c r="I18" t="n">
         <v>901.0275029685348</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>20</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.45</v>
+        <v>-2.04</v>
       </c>
       <c r="L18" t="n">
         <v>2.62</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>5.61</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44974.38541666666</v>
+        <v>44974.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>927.25</v>
+        <v>948</v>
       </c>
       <c r="I19" t="n">
         <v>942.2654050143622</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.09</v>
+        <v>-5.4</v>
       </c>
       <c r="L19" t="n">
-        <v>5.64</v>
+        <v>5.72</v>
       </c>
       <c r="M19" t="n">
         <v>2.02</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>4.8</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44994.38541666666</v>
+        <v>44994.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>909.95</v>
+        <v>904</v>
       </c>
       <c r="I20" t="n">
         <v>904.0908743003132</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.01</v>
+        <v>-4.64</v>
       </c>
       <c r="L20" t="n">
-        <v>4.81</v>
+        <v>4.85</v>
       </c>
       <c r="M20" t="n">
         <v>0.42</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>4.82</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45001.55208333334</v>
+        <v>45002.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>937.15</v>
+        <v>949.55</v>
       </c>
       <c r="I21" t="n">
         <v>945.8646148609878</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.67</v>
+        <v>-5.04</v>
       </c>
       <c r="L21" t="n">
-        <v>3.86</v>
+        <v>5.09</v>
       </c>
       <c r="M21" t="n">
         <v>0.03</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.93</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45040.55208333334</v>
+        <v>45041.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>990</v>
+        <v>956.5</v>
       </c>
       <c r="I22" t="n">
         <v>959.7326652280309</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K22" t="n">
-        <v>4.26</v>
+        <v>0.73</v>
       </c>
       <c r="L22" t="n">
         <v>2.61</v>
@@ -1695,7 +1958,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>1.27</v>
+        <v>2.73</v>
       </c>
       <c r="O22" t="n">
         <v>1.01</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.58</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45055.55208333334</v>
+        <v>45056.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>950</v>
+        <v>963.15</v>
       </c>
       <c r="I23" t="n">
         <v>955.1228460019255</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>0.68</v>
+        <v>-0.7</v>
       </c>
       <c r="L23" t="n">
         <v>3.67</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.05</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45100.55208333334</v>
+        <v>45103.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1033.5</v>
+        <v>1031.9</v>
       </c>
       <c r="I24" t="n">
         <v>1033.244265930423</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K24" t="n">
-        <v>7.3</v>
+        <v>7.14</v>
       </c>
       <c r="L24" t="n">
         <v>1.57</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>4.63</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45105.55208333334</v>
+        <v>45107.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1062</v>
+        <v>1080.3</v>
       </c>
       <c r="I25" t="n">
         <v>1073.634709202459</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.92</v>
+        <v>-4.69</v>
       </c>
       <c r="L25" t="n">
-        <v>4.81</v>
+        <v>5.53</v>
       </c>
       <c r="M25" t="n">
-        <v>0.68</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>2.13</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>4.8</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45131.38541666666</v>
+        <v>45131.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>1040</v>
+        <v>1031.3</v>
       </c>
       <c r="I26" t="n">
         <v>1039.014184374282</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.73</v>
+        <v>-4.54</v>
       </c>
       <c r="L26" t="n">
-        <v>4.19</v>
+        <v>4.64</v>
       </c>
       <c r="M26" t="n">
         <v>0.6</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.86</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45215.55208333334</v>
+        <v>45216.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>985</v>
+        <v>1005.2</v>
       </c>
       <c r="I27" t="n">
         <v>1001.740444757786</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>84</v>
+        <v>84.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>4.49</v>
+        <v>2.53</v>
       </c>
       <c r="L27" t="n">
         <v>1.62</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>4.25</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45224.55208333334</v>
+        <v>45225.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>976</v>
+        <v>964.75</v>
       </c>
       <c r="I28" t="n">
         <v>967.6700360462179</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.9</v>
+        <v>-4.02</v>
       </c>
       <c r="L28" t="n">
-        <v>3.22</v>
+        <v>4.52</v>
       </c>
       <c r="M28" t="n">
         <v>0.3</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>4.46</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45232.55208333334</v>
+        <v>45233.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>989.05</v>
+        <v>1010.6</v>
       </c>
       <c r="I29" t="n">
         <v>1000.998179832414</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.52</v>
+        <v>-4.75</v>
       </c>
       <c r="L29" t="n">
-        <v>4.43</v>
+        <v>5.1</v>
       </c>
       <c r="M29" t="n">
         <v>2.58</v>
       </c>
       <c r="N29" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
         <v>-1.39</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.96</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45242.76041666666</v>
+        <v>45243.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>986</v>
+        <v>979.95</v>
       </c>
       <c r="I30" t="n">
         <v>981.3978576263513</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>9.375</v>
+        <v>10</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.43</v>
+        <v>-3.03</v>
       </c>
       <c r="L30" t="n">
         <v>3.42</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>4.22</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45260.55208333334</v>
+        <v>45261.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1011.9</v>
+        <v>1022.4</v>
       </c>
       <c r="I31" t="n">
         <v>1013.481528325249</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.26</v>
+        <v>-4.33</v>
       </c>
       <c r="L31" t="n">
-        <v>4.18</v>
+        <v>5.01</v>
       </c>
       <c r="M31" t="n">
         <v>0.8100000000000001</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>3.98</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45300.38541666666</v>
+        <v>45300.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>1182</v>
+        <v>1159</v>
       </c>
       <c r="I32" t="n">
         <v>1162.617563590259</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>15.61</v>
+        <v>13.36</v>
       </c>
       <c r="L32" t="n">
         <v>1.41</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.01</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45314.55208333334</v>
+        <v>45315.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1128.45</v>
+        <v>1160.35</v>
       </c>
       <c r="I33" t="n">
         <v>1159.328406675093</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>2.64</v>
+        <v>-0.12</v>
       </c>
       <c r="L33" t="n">
         <v>2.01</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.9</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1212.95</v>
+        <v>1198.35</v>
       </c>
       <c r="I34" t="n">
         <v>1205.116438119799</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K34" t="n">
-        <v>4.53</v>
+        <v>3.27</v>
       </c>
       <c r="L34" t="n">
         <v>3.46</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.01</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45390.38541666666</v>
+        <v>45390.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="I35" t="n">
         <v>1242.001252466896</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.64</v>
+        <v>-3.98</v>
       </c>
       <c r="L35" t="n">
         <v>6.76</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.55</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45442.55208333334</v>
+        <v>45443.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1276.1</v>
+        <v>1265.05</v>
       </c>
       <c r="I36" t="n">
         <v>1268.547561486431</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>52</v>
+        <v>52.83333333333334</v>
       </c>
       <c r="K36" t="n">
-        <v>2.42</v>
+        <v>1.53</v>
       </c>
       <c r="L36" t="n">
         <v>8.5</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>5.91</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45447.38541666666</v>
+        <v>45447.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>1320.7</v>
+        <v>1347</v>
       </c>
       <c r="I37" t="n">
         <v>1328.097845383481</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.4</v>
+        <v>-6.48</v>
       </c>
       <c r="L37" t="n">
-        <v>5.53</v>
+        <v>7.32</v>
       </c>
       <c r="M37" t="n">
         <v>2.39</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45513.55208333334</v>
+        <v>45516.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1444</v>
+        <v>1399</v>
       </c>
       <c r="I38" t="n">
         <v>1425.604582075417</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>66</v>
+        <v>68.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>7.2</v>
+        <v>3.86</v>
       </c>
       <c r="L38" t="n">
         <v>3.7</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.49</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45530.38541666666</v>
+        <v>45530.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>1443.15</v>
+        <v>1451</v>
       </c>
       <c r="I39" t="n">
         <v>1450.01822581896</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.16</v>
+        <v>-3.72</v>
       </c>
       <c r="L39" t="n">
         <v>4.31</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>4.78</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45552.55208333334</v>
+        <v>45553.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1456.1</v>
+        <v>1432.3</v>
       </c>
       <c r="I40" t="n">
         <v>1437.726594159244</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>0.35</v>
+        <v>-1.29</v>
       </c>
       <c r="L40" t="n">
         <v>2.4</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.21</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45621.55208333334</v>
+        <v>45622.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1224.5</v>
+        <v>1242.8</v>
       </c>
       <c r="I41" t="n">
         <v>1237.558261068105</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>68.16666666666667</v>
+        <v>69</v>
       </c>
       <c r="K41" t="n">
-        <v>14.51</v>
+        <v>13.23</v>
       </c>
       <c r="L41" t="n">
         <v>2.59</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>6.26</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45632.55208333334</v>
+        <v>45635.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1230.65</v>
+        <v>1124.85</v>
       </c>
       <c r="I42" t="n">
         <v>1202.391974571068</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.98</v>
+        <v>-9.49</v>
       </c>
       <c r="L42" t="n">
-        <v>2.22</v>
+        <v>11.36</v>
       </c>
       <c r="M42" t="n">
-        <v>1.61</v>
+        <v>4.93</v>
       </c>
       <c r="N42" t="n">
-        <v>1.55</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="O42" t="n">
         <v>1.51</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.51</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1093</v>
+        <v>1103.25</v>
       </c>
       <c r="I43" t="n">
         <v>1101.975494651899</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K43" t="n">
-        <v>2.83</v>
+        <v>1.92</v>
       </c>
       <c r="L43" t="n">
         <v>4.01</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>4.13</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45681.38541666666</v>
+        <v>45681.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1130.9</v>
+        <v>1130</v>
       </c>
       <c r="I44" t="n">
         <v>1130.57374347414</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="L44" t="n">
         <v>1.17</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>5.43</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45688.55208333334</v>
+        <v>45689.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1118.1</v>
+        <v>1206.4</v>
       </c>
       <c r="I45" t="n">
         <v>1173.165985497024</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>1.05</v>
+        <v>-6.76</v>
       </c>
       <c r="L45" t="n">
-        <v>0.7</v>
+        <v>7.48</v>
       </c>
       <c r="M45" t="n">
-        <v>0.03</v>
+        <v>0.78</v>
       </c>
       <c r="N45" t="n">
-        <v>0.36</v>
+        <v>5.98</v>
       </c>
       <c r="O45" t="n">
         <v>-1.17</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45694.55208333334</v>
+        <v>45695.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1120</v>
+        <v>1106.95</v>
       </c>
       <c r="I46" t="n">
         <v>1107.812199826476</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.16</v>
+        <v>-8.24</v>
       </c>
       <c r="L46" t="n">
-        <v>7.51</v>
+        <v>9.27</v>
       </c>
       <c r="M46" t="n">
         <v>0.84</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.29</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45723.55208333334</v>
+        <v>45726.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1044.7</v>
+        <v>1049.35</v>
       </c>
       <c r="I47" t="n">
         <v>1046.380584213778</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>5.62</v>
+        <v>5.2</v>
       </c>
       <c r="L47" t="n">
         <v>5.7</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.78</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45805.55208333334</v>
+        <v>45806.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1251.9</v>
+        <v>1229.3</v>
       </c>
       <c r="I48" t="n">
         <v>1239.473219672499</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>79.16666666666667</v>
+        <v>80</v>
       </c>
       <c r="K48" t="n">
-        <v>19.3</v>
+        <v>17.15</v>
       </c>
       <c r="L48" t="n">
         <v>2.76</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>6.07</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45842.55208333334</v>
+        <v>45845.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1198</v>
+        <v>1264.5</v>
       </c>
       <c r="I49" t="n">
         <v>1206.392520680584</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K49" t="n">
-        <v>2.55</v>
+        <v>-2.86</v>
       </c>
       <c r="L49" t="n">
         <v>5.86</v>
       </c>
       <c r="M49" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="N49" t="n">
-        <v>2.66</v>
+        <v>5.93</v>
       </c>
       <c r="O49" t="n">
         <v>-0.7</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.9</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45859.38541666666</v>
+        <v>45859.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="I50" t="n">
         <v>1241.053334920008</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.54</v>
+        <v>-1.94</v>
       </c>
       <c r="L50" t="n">
         <v>3.11</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>3.8</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45868.55208333334</v>
+        <v>45869.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1216.1</v>
+        <v>1253.6</v>
       </c>
       <c r="I51" t="n">
         <v>1251.431021641836</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K51" t="n">
-        <v>1.93</v>
+        <v>-1.1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.79</v>
+        <v>1.21</v>
       </c>
       <c r="M51" t="n">
         <v>0.2</v>
       </c>
       <c r="N51" t="n">
-        <v>0.55</v>
+        <v>3.53</v>
       </c>
       <c r="O51" t="n">
         <v>-1</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>5.97</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45874.55208333334</v>
+        <v>45875.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1224.3</v>
+        <v>1205</v>
       </c>
       <c r="I52" t="n">
         <v>1221.853372127641</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.34</v>
+        <v>-3.88</v>
       </c>
       <c r="L52" t="n">
-        <v>3.87</v>
+        <v>5.23</v>
       </c>
       <c r="M52" t="n">
         <v>0.72</v>
       </c>
       <c r="N52" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="O52" t="n">
         <v>3.53</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>5.58</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1218.7</v>
+        <v>1240.6</v>
       </c>
       <c r="I53" t="n">
         <v>1240.472961455385</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.14</v>
+        <v>-2.95</v>
       </c>
       <c r="L53" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="M53" t="n">
         <v>1.91</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>6.21</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45922.55208333334</v>
+        <v>45923.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1230.1</v>
+        <v>1198.8</v>
       </c>
       <c r="I54" t="n">
         <v>1216.085043940477</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.85</v>
+        <v>-3.37</v>
       </c>
       <c r="L54" t="n">
-        <v>2.39</v>
+        <v>3.56</v>
       </c>
       <c r="M54" t="n">
         <v>0.8</v>
       </c>
       <c r="N54" t="n">
-        <v>2.43</v>
+        <v>3.08</v>
       </c>
       <c r="O54" t="n">
         <v>2.17</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>6.05</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45961.55208333334</v>
+        <v>45964.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1119.9</v>
+        <v>1173.4</v>
       </c>
       <c r="I55" t="n">
         <v>1142.456819420133</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K55" t="n">
-        <v>6.58</v>
+        <v>2.12</v>
       </c>
       <c r="L55" t="n">
         <v>2.97</v>
       </c>
       <c r="M55" t="n">
-        <v>0.57</v>
+        <v>2.51</v>
       </c>
       <c r="N55" t="n">
-        <v>1.7</v>
+        <v>5.19</v>
       </c>
       <c r="O55" t="n">
         <v>-3.08</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.47</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45985.38541666666</v>
+        <v>45985.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1124.8</v>
+        <v>1108.4</v>
       </c>
       <c r="I56" t="n">
         <v>1118.895597200605</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.14</v>
+        <v>-5.54</v>
       </c>
       <c r="L56" t="n">
-        <v>5.11</v>
+        <v>5.55</v>
       </c>
       <c r="M56" t="n">
         <v>0.6899999999999999</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.51</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46003.55208333334</v>
+        <v>46006.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1149.6</v>
+        <v>1159.3</v>
       </c>
       <c r="I57" t="n">
         <v>1158.384902088719</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.72</v>
+        <v>-4.59</v>
       </c>
       <c r="L57" t="n">
         <v>5.33</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>4.5</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46045.55208333334</v>
+        <v>46049.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1242.7</v>
+        <v>1169.1</v>
       </c>
       <c r="I58" t="n">
         <v>1205.536568562093</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K58" t="n">
-        <v>7.19</v>
+        <v>0.85</v>
       </c>
       <c r="L58" t="n">
-        <v>1.31</v>
+        <v>3.64</v>
       </c>
       <c r="M58" t="n">
-        <v>0.32</v>
+        <v>1.09</v>
       </c>
       <c r="N58" t="n">
-        <v>0.74</v>
+        <v>5.21</v>
       </c>
       <c r="O58" t="n">
         <v>1.72</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.58</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46071.38541666666</v>
+        <v>46071.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>1211.9</v>
+        <v>1217.7</v>
       </c>
       <c r="I59" t="n">
         <v>1216.737980881354</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.66</v>
+        <v>-4.16</v>
       </c>
       <c r="L59" t="n">
         <v>5.13</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>4.22</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1214.9</v>
+        <v>1170</v>
       </c>
       <c r="I60" t="n">
         <v>1193.17721444453</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.23</v>
+        <v>-3.92</v>
       </c>
       <c r="L60" t="n">
-        <v>2.77</v>
+        <v>3.97</v>
       </c>
       <c r="M60" t="n">
-        <v>0.01</v>
+        <v>2.05</v>
       </c>
       <c r="N60" t="n">
-        <v>2.68</v>
+        <v>3.13</v>
       </c>
       <c r="O60" t="n">
         <v>0.08</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>6.09</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1026.15</v>
+        <v>1077.1</v>
       </c>
       <c r="I61" t="n">
         <v>1041.933810272855</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K61" t="n">
-        <v>12.29</v>
+        <v>7.94</v>
       </c>
       <c r="L61" t="n">
         <v>2.87</v>
       </c>
       <c r="M61" t="n">
-        <v>2.17</v>
+        <v>3.84</v>
       </c>
       <c r="N61" t="n">
-        <v>2.78</v>
+        <v>4.57</v>
       </c>
       <c r="O61" t="n">
         <v>-3.13</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.77</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1091.2</v>
+        <v>1062.55</v>
       </c>
       <c r="I62" t="n">
         <v>1081.678157003417</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K62" t="n">
-        <v>1.31</v>
+        <v>-1.35</v>
       </c>
       <c r="L62" t="n">
         <v>3.49</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.79</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1035.5</v>
+        <v>1043.7</v>
       </c>
       <c r="I63" t="n">
         <v>1036.734678693275</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K63" t="n">
-        <v>2.55</v>
+        <v>1.77</v>
       </c>
       <c r="L63" t="n">
         <v>5.6</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>4.48</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46223.55208333334</v>
+        <v>46224.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1066.3</v>
+        <v>1041.6</v>
       </c>
       <c r="I64" t="n">
         <v>1047.219407272947</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K64" t="n">
-        <v>2.17</v>
+        <v>-0.2</v>
       </c>
       <c r="L64" t="n">
         <v>4.69</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.71</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46301.38541666666</v>
+        <v>46301.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>860.45</v>
+        <v>870.75</v>
       </c>
       <c r="I65" t="n">
         <v>866.2775758267428</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>77</v>
+        <v>77.16666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>17.39</v>
+        <v>16.4</v>
       </c>
       <c r="L65" t="n">
         <v>5.61</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>4.73</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46318.55208333334</v>
+        <v>46321.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>845</v>
+        <v>831.5</v>
       </c>
       <c r="I66" t="n">
         <v>833.1102093795829</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.96</v>
+        <v>-4.51</v>
       </c>
       <c r="L66" t="n">
-        <v>3.88</v>
+        <v>5.02</v>
       </c>
       <c r="M66" t="n">
         <v>0.92</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,12 @@
       <c r="Q67" t="n">
         <v>4</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6365,7 +7174,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.8</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="6">
@@ -6375,7 +7184,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -6385,7 +7194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="8">
@@ -6395,7 +7204,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -6405,7 +7214,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -6415,7 +7224,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50.5</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="11">
@@ -6425,7 +7234,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -6435,7 +7244,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -6445,7 +7254,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66.2</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6455,7 +7264,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="15">
@@ -6465,7 +7274,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.67</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="16">
@@ -6475,7 +7284,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.74</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="17">
@@ -6485,7 +7294,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19.3</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="18">
@@ -6495,7 +7304,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.8</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="19">
@@ -6505,7 +7314,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.8</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="20">
@@ -6515,7 +7324,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.67</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="21">
@@ -6525,7 +7334,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.5</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="22">
@@ -6535,7 +7344,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -6545,7 +7354,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -6555,7 +7364,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="25">
@@ -6575,7 +7384,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.68</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="27">
@@ -6585,7 +7394,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.08</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -6595,7 +7404,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
